--- a/su25beetleegg1.xlsx
+++ b/su25beetleegg1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{570EA8BE-C462-489A-ABF9-4C64F3F19139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E50350-AFBF-4B85-8828-223395D0BF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F047FC30-8602-432A-8CD7-B90CBC222496}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{F047FC30-8602-432A-8CD7-B90CBC222496}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
   <si>
     <t>Treatment</t>
   </si>
@@ -44,21 +44,12 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>Date_Beetle_Added</t>
-  </si>
-  <si>
     <t>Egg_mass_#</t>
   </si>
   <si>
-    <t>Date_Laid</t>
-  </si>
-  <si>
     <t>#_Eggs</t>
   </si>
   <si>
-    <t>Date_Hatched</t>
-  </si>
-  <si>
     <t>Hatched</t>
   </si>
   <si>
@@ -68,9 +59,6 @@
     <t>C-MBB-2</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -102,6 +90,18 @@
   </si>
   <si>
     <t>MP-Pf-5</t>
+  </si>
+  <si>
+    <t>Eggs_hatched</t>
+  </si>
+  <si>
+    <t>Adults</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>egg_mass_#</t>
   </si>
 </sst>
 </file>
@@ -144,12 +144,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,15 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCD1C90-74DF-4417-B5AC-49080762C2A8}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,67 +503,42 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>45862</v>
-      </c>
       <c r="F2">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>45863</v>
-      </c>
-      <c r="F3">
-        <v>59</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45870</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -578,346 +547,367 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>45868</v>
-      </c>
       <c r="F4">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45878</v>
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>45864</v>
-      </c>
       <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2">
-        <v>45874</v>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45858</v>
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
       </c>
       <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <v>45865</v>
-      </c>
-      <c r="F6">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="H6" t="s">
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2">
-        <v>45865</v>
-      </c>
-      <c r="F7">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
-        <v>45867</v>
-      </c>
-      <c r="F8">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
-        <v>45858</v>
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" s="2">
-        <v>45884</v>
+      <c r="E9" t="s">
+        <v>7</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9">
         <v>2</v>
       </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>45868</v>
-      </c>
       <c r="F10">
-        <v>15</v>
-      </c>
-      <c r="G10" s="2">
-        <v>45875</v>
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F11">
+        <v>37</v>
+      </c>
+      <c r="G11">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
         <v>17</v>
       </c>
-      <c r="C11" s="2">
-        <v>45858</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>45872</v>
-      </c>
-      <c r="F11">
-        <v>64</v>
-      </c>
-      <c r="G11" s="2">
-        <v>45879</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="E12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <v>17</v>
       </c>
-      <c r="C12" s="2">
-        <v>45865</v>
-      </c>
-      <c r="D12">
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
         <v>2</v>
-      </c>
-      <c r="E12" s="2">
-        <v>45884</v>
-      </c>
-      <c r="F12">
-        <v>17</v>
-      </c>
-      <c r="G12" s="2">
-        <v>45888</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2">
-        <v>45865</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>45874</v>
-      </c>
-      <c r="F13">
-        <v>17</v>
-      </c>
-      <c r="G13" s="2">
-        <v>45882</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2">
-        <v>45865</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="2">
-        <v>45878</v>
+      <c r="E14" t="s">
+        <v>7</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14">
         <v>2</v>
       </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2">
-        <v>45865</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2">
-        <v>45870</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2">
-        <v>45865</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2">
-        <v>45872</v>
-      </c>
-      <c r="F16">
-        <v>11</v>
-      </c>
-      <c r="G16" t="s">
-        <v>10</v>
-      </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -926,23 +916,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -1175,25 +1148,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9433B926-72D4-4350-95F8-2CFB1C4C6ED7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B60D668-D6A6-4D3B-B4DE-5D3D90521FA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9797B1E7-8EC4-4FBE-817F-9D760DC08D64}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1212,6 +1184,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B60D668-D6A6-4D3B-B4DE-5D3D90521FA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9433B926-72D4-4350-95F8-2CFB1C4C6ED7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" contentBits="0" removed="0"/>
